--- a/output/pdf_financials_xlsx/GPG.xlsx
+++ b/output/pdf_financials_xlsx/GPG.xlsx
@@ -5976,37 +5976,37 @@
         <v>1.744517</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.744517</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.744517</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.842517</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.958245</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.457054</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.633829</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.255579</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.795379</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.242279</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.695654</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>5.111354</v>
       </c>
     </row>
     <row r="93">
@@ -10207,7 +10207,11 @@
           <t>RESERVES 7</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11589,7 +11593,11 @@
           <t>RESERVES 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11684,7 +11692,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12373,7 +12385,11 @@
           <t>RESERVES</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GPG.xlsx
+++ b/output/pdf_financials_xlsx/GPG.xlsx
@@ -2437,28 +2437,28 @@
         <v>0.19673</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.544024</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.135613</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.304379</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.400393</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.318007</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.344159</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.616804</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>2.48524</v>
       </c>
     </row>
     <row r="35">
@@ -2553,28 +2553,28 @@
         <v>0.198283</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.001035</v>
+        <v>0.545059</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0042</v>
+        <v>0.139813</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.002171</v>
+        <v>0.30655</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.000949</v>
+        <v>3.401342</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.01298</v>
+        <v>2.330987</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.344159</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.616804</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>1.5</v>
+        <v>3.98524</v>
       </c>
     </row>
     <row r="37">
@@ -3249,28 +3249,28 @@
         <v>0.01592</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.58001</v>
+        <v>0.035986</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.432577</v>
+        <v>0.296964</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.34174</v>
+        <v>0.037361</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.483748</v>
+        <v>0.083355</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.370707</v>
+        <v>0.0527</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.398023</v>
+        <v>0.053864</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.7680630000000001</v>
+        <v>0.151259</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>2.555418</v>
+        <v>0.070178</v>
       </c>
     </row>
     <row r="49">
@@ -7840,10 +7840,10 @@
         <v>0</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.049677</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.07285899999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7898,10 +7898,10 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.049677</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.07285899999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14660,7 +14660,11 @@
           <t>Reclamation deposits 6</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -20711,7 +20715,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GPG.xlsx
+++ b/output/pdf_financials_xlsx/GPG.xlsx
@@ -783,19 +783,19 @@
         <v>0.305042</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.389437</v>
+        <v>0.429437</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.42546</v>
+        <v>0.46546</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.452216</v>
+        <v>0.492216</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.387245</v>
+        <v>0.427245</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.4631</v>
+        <v>0.5031</v>
       </c>
     </row>
     <row r="8">
@@ -957,19 +957,19 @@
         <v>0.308745</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.394586</v>
+        <v>0.434586</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.471022</v>
+        <v>0.511022</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.504414</v>
+        <v>0.544414</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.417776</v>
+        <v>0.457776</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.516496</v>
+        <v>0.556496</v>
       </c>
     </row>
     <row r="11">
@@ -1281,7 +1281,7 @@
         <v>-1.88913</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-1.243848</v>
+        <v>-2.487696</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>-1.317893</v>
@@ -1336,10 +1336,10 @@
         <v>0.417907</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.497433</v>
+        <v>1.902288</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>1.243848</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1999,7 +1999,7 @@
         <v>-1.88913</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.243848</v>
+        <v>-2.487696</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.317893</v>
@@ -2115,7 +2115,7 @@
         <v>-1.88913</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.243848</v>
+        <v>-2.487696</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.317893</v>
@@ -2262,10 +2262,10 @@
         <v>17.86862780729228</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-26.33132711883248</v>
+        <v>-100.6965110924076</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7216,13 +7216,13 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-2.1</v>
       </c>
       <c r="D114" s="3" t="n">
-        <v>0</v>
+        <v>-0.02716</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="F114" s="3" t="n">
         <v>0</v>
@@ -7277,22 +7277,22 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.717773</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.149909</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.018946</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.20304</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.192355</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.06494800000000001</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -8419,7 +8419,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8477,7 +8477,7 @@
         <v>-0.000214</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.256055</v>
+        <v>-0.281055</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.291089</v>
@@ -22550,7 +22550,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -25142,7 +25146,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -26958,7 +26966,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28687,7 +28699,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29919,7 +29935,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr"/>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -30119,7 +30139,11 @@
           <t>Purchases of marketable securities</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -31749,7 +31773,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -31846,7 +31874,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -33458,7 +33490,11 @@
           <t>Future income tax expense</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -37416,7 +37452,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -39409,7 +39449,11 @@
           <t>Directors’ fees 9</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -46991,7 +47035,11 @@
           <t>Loss Before Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E388" t="inlineStr">
         <is>
           <t>-</t>
@@ -47090,7 +47138,11 @@
           <t>Deferred Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -52962,7 +53014,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
